--- a/artfynd/A 20765-2024 artfynd.xlsx
+++ b/artfynd/A 20765-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117980630</v>
+        <v>117980700</v>
       </c>
       <c r="B2" t="n">
-        <v>97740</v>
+        <v>97753</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593384</v>
+        <v>593387</v>
       </c>
       <c r="R2" t="n">
-        <v>6982128</v>
+        <v>6982144</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117980700</v>
+        <v>117980630</v>
       </c>
       <c r="B6" t="n">
-        <v>97753</v>
+        <v>97740</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593387</v>
+        <v>593384</v>
       </c>
       <c r="R6" t="n">
-        <v>6982144</v>
+        <v>6982128</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>

--- a/artfynd/A 20765-2024 artfynd.xlsx
+++ b/artfynd/A 20765-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117980700</v>
       </c>
       <c r="B2" t="n">
-        <v>97753</v>
+        <v>97755</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117980652</v>
+        <v>117980630</v>
       </c>
       <c r="B3" t="n">
-        <v>79561</v>
+        <v>97742</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593365</v>
+        <v>593384</v>
       </c>
       <c r="R3" t="n">
-        <v>6982134</v>
+        <v>6982128</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -882,7 +882,7 @@
         <v>117980617</v>
       </c>
       <c r="B4" t="n">
-        <v>57440</v>
+        <v>57441</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117980651</v>
+        <v>117980652</v>
       </c>
       <c r="B5" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593362</v>
+        <v>593365</v>
       </c>
       <c r="R5" t="n">
-        <v>6982126</v>
+        <v>6982134</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117980630</v>
+        <v>117980651</v>
       </c>
       <c r="B6" t="n">
-        <v>97740</v>
+        <v>79563</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593384</v>
+        <v>593362</v>
       </c>
       <c r="R6" t="n">
-        <v>6982128</v>
+        <v>6982126</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>

--- a/artfynd/A 20765-2024 artfynd.xlsx
+++ b/artfynd/A 20765-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117980700</v>
+        <v>117980617</v>
       </c>
       <c r="B2" t="n">
-        <v>97755</v>
+        <v>57441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593387</v>
+        <v>593318</v>
       </c>
       <c r="R2" t="n">
-        <v>6982144</v>
+        <v>6982203</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117980630</v>
+        <v>117980700</v>
       </c>
       <c r="B3" t="n">
-        <v>97742</v>
+        <v>97755</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593384</v>
+        <v>593387</v>
       </c>
       <c r="R3" t="n">
-        <v>6982128</v>
+        <v>6982144</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117980617</v>
+        <v>117980630</v>
       </c>
       <c r="B4" t="n">
-        <v>57441</v>
+        <v>97742</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220093</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593318</v>
+        <v>593384</v>
       </c>
       <c r="R4" t="n">
-        <v>6982203</v>
+        <v>6982128</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
